--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381241</v>
+        <v>113381194</v>
       </c>
       <c r="B20" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,11 +2886,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793632</v>
+        <v>793567</v>
       </c>
       <c r="R20" t="n">
-        <v>7193093</v>
+        <v>7192914</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2941,6 +2937,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381227</v>
+        <v>113381130</v>
       </c>
       <c r="B21" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3012,14 +3013,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793555</v>
+        <v>793621</v>
       </c>
       <c r="R21" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3056,7 +3057,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381194</v>
+        <v>113381216</v>
       </c>
       <c r="B22" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3132,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793567</v>
+        <v>793563</v>
       </c>
       <c r="R22" t="n">
-        <v>7192914</v>
+        <v>7192909</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket bladrosetter</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381216</v>
+        <v>113381227</v>
       </c>
       <c r="B23" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3248,7 +3249,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793563</v>
+        <v>793555</v>
       </c>
       <c r="R23" t="n">
         <v>7192909</v>
@@ -3288,7 +3289,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381146</v>
+        <v>113381241</v>
       </c>
       <c r="B24" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3349,7 +3350,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -3364,10 +3369,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793636</v>
+        <v>793632</v>
       </c>
       <c r="R24" t="n">
-        <v>7193062</v>
+        <v>7193093</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3400,11 +3405,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381130</v>
+        <v>113381146</v>
       </c>
       <c r="B25" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3476,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793621</v>
+        <v>793636</v>
       </c>
       <c r="R25" t="n">
-        <v>7193074</v>
+        <v>7193062</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,7 +2853,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381194</v>
+        <v>113381241</v>
       </c>
       <c r="B20" t="n">
         <v>97314</v>
@@ -2886,7 +2886,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2901,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793567</v>
+        <v>793632</v>
       </c>
       <c r="R20" t="n">
-        <v>7192914</v>
+        <v>7193093</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2937,11 +2941,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,7 +2968,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381130</v>
+        <v>113381216</v>
       </c>
       <c r="B21" t="n">
         <v>97314</v>
@@ -3013,14 +3012,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793621</v>
+        <v>793563</v>
       </c>
       <c r="R21" t="n">
-        <v>7193074</v>
+        <v>7192909</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3057,7 +3056,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381216</v>
+        <v>113381194</v>
       </c>
       <c r="B22" t="n">
         <v>97314</v>
@@ -3133,10 +3132,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793563</v>
+        <v>793567</v>
       </c>
       <c r="R22" t="n">
-        <v>7192909</v>
+        <v>7192914</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3173,7 +3172,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3317,7 +3316,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381241</v>
+        <v>113381146</v>
       </c>
       <c r="B24" t="n">
         <v>97314</v>
@@ -3350,11 +3349,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -3369,10 +3364,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793632</v>
+        <v>793636</v>
       </c>
       <c r="R24" t="n">
-        <v>7193093</v>
+        <v>7193062</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3405,6 +3400,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,7 +3432,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381146</v>
+        <v>113381130</v>
       </c>
       <c r="B25" t="n">
         <v>97314</v>
@@ -3476,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793636</v>
+        <v>793621</v>
       </c>
       <c r="R25" t="n">
-        <v>7193062</v>
+        <v>7193074</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381241</v>
+        <v>113381227</v>
       </c>
       <c r="B20" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,11 +2886,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793632</v>
+        <v>793555</v>
       </c>
       <c r="R20" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2941,6 +2937,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381216</v>
+        <v>113381130</v>
       </c>
       <c r="B21" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3012,14 +3013,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793563</v>
+        <v>793621</v>
       </c>
       <c r="R21" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3056,7 +3057,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381194</v>
+        <v>113381216</v>
       </c>
       <c r="B22" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3132,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793567</v>
+        <v>793563</v>
       </c>
       <c r="R22" t="n">
-        <v>7192914</v>
+        <v>7192909</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket bladrosetter</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381227</v>
+        <v>113381146</v>
       </c>
       <c r="B23" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793555</v>
+        <v>793636</v>
       </c>
       <c r="R23" t="n">
-        <v>7192909</v>
+        <v>7193062</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3288,7 +3289,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381146</v>
+        <v>113381194</v>
       </c>
       <c r="B24" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3364,10 +3365,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793636</v>
+        <v>793567</v>
       </c>
       <c r="R24" t="n">
-        <v>7193062</v>
+        <v>7192914</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3404,7 +3405,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3433,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B25" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,7 +3466,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -3476,14 +3481,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R25" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3516,11 +3521,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,7 +2853,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381227</v>
+        <v>113381216</v>
       </c>
       <c r="B20" t="n">
         <v>97326</v>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793555</v>
+        <v>793563</v>
       </c>
       <c r="R20" t="n">
         <v>7192909</v>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,7 +2969,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381130</v>
+        <v>113381146</v>
       </c>
       <c r="B21" t="n">
         <v>97326</v>
@@ -3013,14 +3013,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793621</v>
+        <v>793636</v>
       </c>
       <c r="R21" t="n">
-        <v>7193074</v>
+        <v>7193062</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381216</v>
+        <v>113381227</v>
       </c>
       <c r="B22" t="n">
         <v>97326</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793563</v>
+        <v>793555</v>
       </c>
       <c r="R22" t="n">
         <v>7192909</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,7 +3201,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381146</v>
+        <v>113381194</v>
       </c>
       <c r="B23" t="n">
         <v>97326</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793636</v>
+        <v>793567</v>
       </c>
       <c r="R23" t="n">
-        <v>7193062</v>
+        <v>7192914</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,7 +3317,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381194</v>
+        <v>113381130</v>
       </c>
       <c r="B24" t="n">
         <v>97326</v>
@@ -3361,14 +3361,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793567</v>
+        <v>793621</v>
       </c>
       <c r="R24" t="n">
-        <v>7192914</v>
+        <v>7193074</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mycket bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381216</v>
+        <v>113381146</v>
       </c>
       <c r="B20" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793563</v>
+        <v>793636</v>
       </c>
       <c r="R20" t="n">
-        <v>7192909</v>
+        <v>7193062</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381146</v>
+        <v>113381227</v>
       </c>
       <c r="B21" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793636</v>
+        <v>793555</v>
       </c>
       <c r="R21" t="n">
-        <v>7193062</v>
+        <v>7192909</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381227</v>
+        <v>113381194</v>
       </c>
       <c r="B22" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793555</v>
+        <v>793567</v>
       </c>
       <c r="R22" t="n">
-        <v>7192909</v>
+        <v>7192914</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381194</v>
+        <v>113381216</v>
       </c>
       <c r="B23" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793567</v>
+        <v>793563</v>
       </c>
       <c r="R23" t="n">
-        <v>7192914</v>
+        <v>7192909</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mycket bladrosetter</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B24" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3350,7 +3350,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -3361,14 +3365,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R24" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3401,11 +3405,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3433,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381241</v>
+        <v>113381130</v>
       </c>
       <c r="B25" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3466,11 +3465,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -3481,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793632</v>
+        <v>793621</v>
       </c>
       <c r="R25" t="n">
-        <v>7193093</v>
+        <v>7193074</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3521,6 +3516,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>113381146</v>
       </c>
       <c r="B20" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>113381227</v>
       </c>
       <c r="B21" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>113381194</v>
       </c>
       <c r="B22" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381216</v>
+        <v>113381130</v>
       </c>
       <c r="B23" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3245,14 +3245,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793563</v>
+        <v>793621</v>
       </c>
       <c r="R23" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381241</v>
+        <v>113381216</v>
       </c>
       <c r="B24" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3350,11 +3350,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -3369,10 +3365,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793632</v>
+        <v>793563</v>
       </c>
       <c r="R24" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3405,6 +3401,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3433,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B25" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,7 +3466,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -3476,14 +3481,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R25" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3516,11 +3521,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,7 +2853,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381146</v>
+        <v>113381194</v>
       </c>
       <c r="B20" t="n">
         <v>97352</v>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793636</v>
+        <v>793567</v>
       </c>
       <c r="R20" t="n">
-        <v>7193062</v>
+        <v>7192914</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,7 +2969,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381227</v>
+        <v>113381130</v>
       </c>
       <c r="B21" t="n">
         <v>97352</v>
@@ -3013,14 +3013,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793555</v>
+        <v>793621</v>
       </c>
       <c r="R21" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,7 +3085,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381194</v>
+        <v>113381146</v>
       </c>
       <c r="B22" t="n">
         <v>97352</v>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793567</v>
+        <v>793636</v>
       </c>
       <c r="R22" t="n">
-        <v>7192914</v>
+        <v>7193062</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,7 +3201,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B23" t="n">
         <v>97352</v>
@@ -3234,7 +3234,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -3245,14 +3249,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R23" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3285,11 +3289,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,7 +3316,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381216</v>
+        <v>113381227</v>
       </c>
       <c r="B24" t="n">
         <v>97352</v>
@@ -3365,7 +3364,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793563</v>
+        <v>793555</v>
       </c>
       <c r="R24" t="n">
         <v>7192909</v>
@@ -3405,7 +3404,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3433,7 +3432,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381241</v>
+        <v>113381216</v>
       </c>
       <c r="B25" t="n">
         <v>97352</v>
@@ -3466,11 +3465,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793632</v>
+        <v>793563</v>
       </c>
       <c r="R25" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3521,6 +3516,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2856,7 +2856,7 @@
         <v>113381194</v>
       </c>
       <c r="B20" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B21" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3002,7 +3002,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -3013,14 +3017,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R21" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3053,11 +3057,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3088,7 +3087,7 @@
         <v>113381146</v>
       </c>
       <c r="B22" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3201,10 +3200,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381241</v>
+        <v>113381227</v>
       </c>
       <c r="B23" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3234,11 +3233,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -3253,10 +3248,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793632</v>
+        <v>793555</v>
       </c>
       <c r="R23" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3289,6 +3284,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381227</v>
+        <v>113381216</v>
       </c>
       <c r="B24" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793555</v>
+        <v>793563</v>
       </c>
       <c r="R24" t="n">
         <v>7192909</v>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381216</v>
+        <v>113381130</v>
       </c>
       <c r="B25" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3476,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793563</v>
+        <v>793621</v>
       </c>
       <c r="R25" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,7 +2853,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381194</v>
+        <v>113381241</v>
       </c>
       <c r="B20" t="n">
         <v>97358</v>
@@ -2886,7 +2886,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2901,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793567</v>
+        <v>793632</v>
       </c>
       <c r="R20" t="n">
-        <v>7192914</v>
+        <v>7193093</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2937,11 +2941,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,7 +2968,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381241</v>
+        <v>113381216</v>
       </c>
       <c r="B21" t="n">
         <v>97358</v>
@@ -3002,11 +3001,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793632</v>
+        <v>793563</v>
       </c>
       <c r="R21" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3057,6 +3052,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381146</v>
+        <v>113381227</v>
       </c>
       <c r="B22" t="n">
         <v>97358</v>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793636</v>
+        <v>793555</v>
       </c>
       <c r="R22" t="n">
-        <v>7193062</v>
+        <v>7192909</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,7 +3200,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381227</v>
+        <v>113381146</v>
       </c>
       <c r="B23" t="n">
         <v>97358</v>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793555</v>
+        <v>793636</v>
       </c>
       <c r="R23" t="n">
-        <v>7192909</v>
+        <v>7193062</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,7 +3316,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381216</v>
+        <v>113381130</v>
       </c>
       <c r="B24" t="n">
         <v>97358</v>
@@ -3360,14 +3360,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793563</v>
+        <v>793621</v>
       </c>
       <c r="R24" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,7 +3432,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381130</v>
+        <v>113381194</v>
       </c>
       <c r="B25" t="n">
         <v>97358</v>
@@ -3476,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793621</v>
+        <v>793567</v>
       </c>
       <c r="R25" t="n">
-        <v>7193074</v>
+        <v>7192914</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381241</v>
+        <v>113381130</v>
       </c>
       <c r="B20" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,11 +2886,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2901,14 +2897,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793632</v>
+        <v>793621</v>
       </c>
       <c r="R20" t="n">
-        <v>7193093</v>
+        <v>7193074</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2941,6 +2937,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381216</v>
+        <v>113381227</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,7 +3017,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793563</v>
+        <v>793555</v>
       </c>
       <c r="R21" t="n">
         <v>7192909</v>
@@ -3056,7 +3057,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381227</v>
+        <v>113381146</v>
       </c>
       <c r="B22" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3132,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793555</v>
+        <v>793636</v>
       </c>
       <c r="R22" t="n">
-        <v>7192909</v>
+        <v>7193062</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381146</v>
+        <v>113381216</v>
       </c>
       <c r="B23" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3248,10 +3249,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793636</v>
+        <v>793563</v>
       </c>
       <c r="R23" t="n">
-        <v>7193062</v>
+        <v>7192909</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3288,7 +3289,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381130</v>
+        <v>113381194</v>
       </c>
       <c r="B24" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3360,14 +3361,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793621</v>
+        <v>793567</v>
       </c>
       <c r="R24" t="n">
-        <v>7193074</v>
+        <v>7192914</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3404,7 +3405,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3433,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381194</v>
+        <v>113381241</v>
       </c>
       <c r="B25" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,7 +3466,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793567</v>
+        <v>793632</v>
       </c>
       <c r="R25" t="n">
-        <v>7192914</v>
+        <v>7193093</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3516,11 +3521,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B20" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,7 +2886,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2897,14 +2901,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R20" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2937,11 +2941,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,10 +2968,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381227</v>
+        <v>113381130</v>
       </c>
       <c r="B21" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3013,14 +3012,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793555</v>
+        <v>793621</v>
       </c>
       <c r="R21" t="n">
-        <v>7192909</v>
+        <v>7193074</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3057,7 +3056,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381146</v>
+        <v>113381227</v>
       </c>
       <c r="B22" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3133,10 +3132,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793636</v>
+        <v>793555</v>
       </c>
       <c r="R22" t="n">
-        <v>7193062</v>
+        <v>7192909</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3173,7 +3172,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mängder av bladrosetter</t>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,10 +3200,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381216</v>
+        <v>113381194</v>
       </c>
       <c r="B23" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3249,10 +3248,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793563</v>
+        <v>793567</v>
       </c>
       <c r="R23" t="n">
-        <v>7192909</v>
+        <v>7192914</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3289,7 +3288,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,10 +3316,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381194</v>
+        <v>113381216</v>
       </c>
       <c r="B24" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3365,10 +3364,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793567</v>
+        <v>793563</v>
       </c>
       <c r="R24" t="n">
-        <v>7192914</v>
+        <v>7192909</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3405,7 +3404,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mycket bladrosetter</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3433,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381241</v>
+        <v>113381146</v>
       </c>
       <c r="B25" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3466,11 +3465,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793632</v>
+        <v>793636</v>
       </c>
       <c r="R25" t="n">
-        <v>7193093</v>
+        <v>7193062</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3521,6 +3516,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113381241</v>
+        <v>113381227</v>
       </c>
       <c r="B20" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,11 +2886,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>793632</v>
+        <v>793555</v>
       </c>
       <c r="R20" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2941,6 +2937,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mängder med rosetter över stor yta</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,7 +2972,7 @@
         <v>113381130</v>
       </c>
       <c r="B21" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3084,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381227</v>
+        <v>113381216</v>
       </c>
       <c r="B22" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3132,7 +3133,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793555</v>
+        <v>793563</v>
       </c>
       <c r="R22" t="n">
         <v>7192909</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mängder med rosetter över stor yta</t>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381194</v>
+        <v>113381241</v>
       </c>
       <c r="B23" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3233,7 +3234,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -3248,10 +3253,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793567</v>
+        <v>793632</v>
       </c>
       <c r="R23" t="n">
-        <v>7192914</v>
+        <v>7193093</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3284,11 +3289,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113381216</v>
+        <v>113381194</v>
       </c>
       <c r="B24" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>793563</v>
+        <v>793567</v>
       </c>
       <c r="R24" t="n">
-        <v>7192909</v>
+        <v>7192914</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3435,7 +3435,7 @@
         <v>113381146</v>
       </c>
       <c r="B25" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -2969,7 +2969,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113381130</v>
+        <v>113381241</v>
       </c>
       <c r="B21" t="n">
         <v>97398</v>
@@ -3002,7 +3002,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -3013,14 +3017,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>793621</v>
+        <v>793632</v>
       </c>
       <c r="R21" t="n">
-        <v>7193074</v>
+        <v>7193093</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3053,11 +3057,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113381216</v>
+        <v>113381146</v>
       </c>
       <c r="B22" t="n">
         <v>97398</v>
@@ -3133,10 +3132,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>793563</v>
+        <v>793636</v>
       </c>
       <c r="R22" t="n">
-        <v>7192909</v>
+        <v>7193062</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3173,7 +3172,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mängder av bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,7 +3200,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113381241</v>
+        <v>113381216</v>
       </c>
       <c r="B23" t="n">
         <v>97398</v>
@@ -3234,11 +3233,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -3253,10 +3248,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>793632</v>
+        <v>793563</v>
       </c>
       <c r="R23" t="n">
-        <v>7193093</v>
+        <v>7192909</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3289,6 +3284,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Många bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3432,7 +3432,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113381146</v>
+        <v>113381130</v>
       </c>
       <c r="B25" t="n">
         <v>97398</v>
@@ -3476,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkberget , Vb</t>
+          <t>Kalkberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>793636</v>
+        <v>793621</v>
       </c>
       <c r="R25" t="n">
-        <v>7193062</v>
+        <v>7193074</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22967-2023 artfynd.xlsx
+++ b/artfynd/A 22967-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2605,7 +2605,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109919829</v>
+        <v>109920045</v>
       </c>
       <c r="B18" t="n">
         <v>96334</v>
@@ -2640,11 +2640,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2653,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>793621.1695299358</v>
+        <v>793566.8739787493</v>
       </c>
       <c r="R18" t="n">
-        <v>7193072.838458724</v>
+        <v>7192923.972403369</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2703,7 +2699,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Många bladrosetter</t>
+          <t>Mindre bestånd</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2731,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109920045</v>
+        <v>113381194</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
+        <v>97650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2766,22 +2762,26 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkberget, Vb</t>
+          <t>Kalkberget , Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>793566.8739787493</v>
+        <v>793567</v>
       </c>
       <c r="R19" t="n">
-        <v>7192923.972403369</v>
+        <v>7192914</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2805,27 +2805,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mindre bestånd</t>
+          <t>Mycket bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,701 +2840,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>113381241</v>
-      </c>
-      <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Kalkberget , Vb</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>793632</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7193093</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>113381216</v>
-      </c>
-      <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Kalkberget , Vb</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>793563</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7192909</v>
-      </c>
-      <c r="S21" t="n">
-        <v>25</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Många bladrosetter</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>113381146</v>
-      </c>
-      <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Kalkberget , Vb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>793636</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7193062</v>
-      </c>
-      <c r="S22" t="n">
-        <v>25</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>113381130</v>
-      </c>
-      <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Kalkberget, Vb</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>793621</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7193074</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mängder av bladrosetter</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>113381227</v>
-      </c>
-      <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Kalkberget , Vb</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>793555</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7192909</v>
-      </c>
-      <c r="S24" t="n">
-        <v>25</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mängder med rosetter över stor yta</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>113381194</v>
-      </c>
-      <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Kalkberget , Vb</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>793567</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7192914</v>
-      </c>
-      <c r="S25" t="n">
-        <v>25</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mycket bladrosetter</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Anders Lundmark</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
